--- a/data/trans_dic/IP1022_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP1022_2023-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen otros</t>
+          <t>Menores que padecen otros (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,64; 8,19</t>
+          <t>0,63; 9,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,55; 12,07</t>
+          <t>1,46; 12,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,71; 8,17</t>
+          <t>1,55; 7,85</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,77; 8,06</t>
+          <t>2,55; 8,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,35; 8,95</t>
+          <t>3,44; 9,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,52; 7,5</t>
+          <t>3,59; 7,92</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,57; 8,13</t>
+          <t>2,38; 8,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,66; 12,55</t>
+          <t>4,75; 11,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,37; 9,12</t>
+          <t>4,25; 8,76</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,6; 15,67</t>
+          <t>5,84; 15,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,04; 16,38</t>
+          <t>5,81; 15,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,6; 13,33</t>
+          <t>6,8; 13,61</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,81; 9,58</t>
+          <t>4,74; 9,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,82; 10,5</t>
+          <t>6,0; 10,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,75; 9,02</t>
+          <t>5,89; 9,2</t>
         </is>
       </c>
     </row>
@@ -803,4 +804,454 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen otros (tasa de respuesta: 99,9%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1562</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3116</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4679</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>359; 5552</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>899; 7748</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1833; 9286</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>7726</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>10389</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>18116</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>4064; 13000</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>6273; 17546</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>12285; 27084</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>8220</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>16561</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>24781</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>4127; 13933</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>10103; 25485</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>16384; 33780</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>26296</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>27561</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>53857</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>16089; 43553</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>17503; 45267</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>39205; 78517</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>43804</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>57628</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>101432</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>31503; 62818</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>45454; 79980</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>83732; 130841</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP1022_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP1022_2023-Edad-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,63; 9,76</t>
+          <t>0,61; 7,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,46; 12,61</t>
+          <t>1,04; 11,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,55; 7,85</t>
+          <t>1,69; 8,14</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,55; 8,16</t>
+          <t>2,8; 8,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,44; 9,61</t>
+          <t>3,16; 8,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,59; 7,92</t>
+          <t>3,63; 7,7</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,38; 8,05</t>
+          <t>2,63; 8,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,75; 11,99</t>
+          <t>4,87; 12,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,25; 8,76</t>
+          <t>4,51; 9,08</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,84; 15,81</t>
+          <t>5,96; 15,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,81; 15,03</t>
+          <t>6,01; 15,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,8; 13,61</t>
+          <t>6,7; 13,75</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,74; 9,45</t>
+          <t>4,86; 9,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,0; 10,56</t>
+          <t>5,81; 10,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,89; 9,2</t>
+          <t>5,85; 9,15</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>359; 5552</t>
+          <t>346; 4359</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>899; 7748</t>
+          <t>638; 7229</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1833; 9286</t>
+          <t>1994; 9632</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4064; 13000</t>
+          <t>4455; 13418</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6273; 17546</t>
+          <t>5763; 16299</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12285; 27084</t>
+          <t>12424; 26325</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4127; 13933</t>
+          <t>4554; 14721</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10103; 25485</t>
+          <t>10357; 25596</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16384; 33780</t>
+          <t>17387; 34993</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>16089; 43553</t>
+          <t>16430; 43884</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17503; 45267</t>
+          <t>18113; 45663</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>39205; 78517</t>
+          <t>38658; 79321</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>31503; 62818</t>
+          <t>32300; 64667</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>45454; 79980</t>
+          <t>44031; 78467</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>83732; 130841</t>
+          <t>83249; 130132</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1022_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP1022_2023-Edad-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,86%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,61; 7,66</t>
+          <t>1,34; 12,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,04; 11,76</t>
+          <t>0,51; 7,46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,69; 8,14</t>
+          <t>1,65; 7,9</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,8; 8,42</t>
+          <t>3,27; 8,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,16; 8,93</t>
+          <t>2,98; 8,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,63; 7,7</t>
+          <t>3,46; 7,47</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,55%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,63; 8,51</t>
+          <t>4,66; 12,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,87; 12,05</t>
+          <t>2,73; 8,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,51; 9,08</t>
+          <t>4,46; 9,31</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>8,21%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,96; 15,93</t>
+          <t>5,25; 11,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,01; 15,16</t>
+          <t>5,76; 12,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,7; 13,75</t>
+          <t>6,17; 10,52</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,74%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,86; 9,73</t>
+          <t>5,5; 9,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,81; 10,36</t>
+          <t>4,89; 8,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,85; 9,15</t>
+          <t>5,63; 8,05</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1562</t>
+          <t>2629</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3116</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4679</t>
+          <t>3931</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>346; 4359</t>
+          <t>680; 6238</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>638; 7229</t>
+          <t>263; 3835</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1994; 9632</t>
+          <t>1681; 8056</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>7726</t>
+          <t>8469</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>10389</t>
+          <t>7655</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>18116</t>
+          <t>16124</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4455; 13418</t>
+          <t>5145; 13463</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5763; 16299</t>
+          <t>4332; 12520</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12424; 26325</t>
+          <t>10500; 22652</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8220</t>
+          <t>15728</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16561</t>
+          <t>8806</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24781</t>
+          <t>24534</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4554; 14721</t>
+          <t>9317; 25346</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10357; 25596</t>
+          <t>4768; 15128</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>17387; 34993</t>
+          <t>16721; 34881</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>26296</t>
+          <t>22200</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>27561</t>
+          <t>22543</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>53857</t>
+          <t>44744</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>16430; 43884</t>
+          <t>15122; 32347</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18113; 45663</t>
+          <t>14790; 31283</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>38658; 79321</t>
+          <t>33632; 57306</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>57</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>43804</t>
+          <t>49026</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>57628</t>
+          <t>40307</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>101432</t>
+          <t>89332</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>32300; 64667</t>
+          <t>38275; 63224</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>44031; 78467</t>
+          <t>30744; 52096</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>83249; 130132</t>
+          <t>74610; 106578</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1022_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP1022_2023-Edad-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que padecen otros (tasa de respuesta: 99,9%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>5,2%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2,53%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3,86%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>1,34; 12,34</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0,51; 7,46</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1,65; 7,9</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>3-7</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>5,38%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>5,26%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>5,32%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>3,27; 8,55</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>2,98; 8,6</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>3,46; 7,47</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>7,86%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>5,04%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>6,55%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>4,66; 12,67</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>2,73; 8,66</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>4,46; 9,31</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>12-15</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>7,7%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>8,79%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>8,21%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>5,25; 11,22</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>5,76; 12,19</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>6,17; 10,52</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>7,04%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>6,42%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>6,74%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>5,5; 9,08</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>4,89; 8,29</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>5,63; 8,05</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.05201827408375412</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.02532280952574411</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.03855501861413151</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>2629</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1302</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>3931</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.01344591908710165</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.005112518141771503</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.01648875369418301</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>680; 6238</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>263; 3835</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1681; 8056</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.1234379387076645</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.07457714942020793</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.07901026425195998</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.05376215677732001</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.05260457866160072</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.05320629436381759</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>8469</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>7655</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>16124</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.03266337409073047</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.02977183253320334</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.03464810020459133</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>5145; 13463</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>4332; 12520</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>10500; 22652</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.08546598123537007</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.08603621952636405</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.07474887928566619</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.07858924994829249</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.05041596444488231</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.06545926912155693</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>15728</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>8806</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>24534</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.04655625680956936</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.02729630416791889</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.04461358930737024</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>9317; 25346</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>4768; 15128</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>16721; 34881</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.1266507787038991</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.08660634733634305</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.09306688749412227</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.07701080338101596</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.08787057762484839</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.08212454624177717</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>22200</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>22543</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>44744</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.05245795967207227</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.05764772261373236</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.06172926841876826</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>15122; 32347</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>14790; 31283</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>33632; 57306</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.1122105277185558</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.1219372964404336</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.1051816133446048</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.07039256836535702</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.06416605638225517</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.06743982926273606</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>49026</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>40307</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>89332</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.05495578711370718</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.04894209517830649</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.0563257980998</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>38275; 63224</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>30744; 52096</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>74610; 106578</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.09077933455002261</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.08293435284411807</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.08045877047757023</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen otros (tasa de respuesta: 99,9%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>2629</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>1302</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>3931</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>680</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>263</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>1681</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>6238</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>3835</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>8056</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>8469</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>7655</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>16124</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>5145</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>4332</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>10500</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>13463</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>12520</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>22652</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>15728</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>8806</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>24534</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>9317</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>4768</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>16721</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>25346</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>15128</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>34881</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>22200</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>22543</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>44744</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>15122</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>14790</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>33632</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>32347</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>31283</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>57306</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>57</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>49026</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>40307</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>89332</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>38275</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>30744</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>74610</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>63224</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>52096</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>106578</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>